--- a/Week05-PreprocessingAndPipelinesSupportVectorMachines/DataScience/data_audit.xlsx
+++ b/Week05-PreprocessingAndPipelinesSupportVectorMachines/DataScience/data_audit.xlsx
@@ -162,10 +162,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>24</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="45605700" cy="44386500"/>
+    <ext cx="7620000" cy="5715000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -173,6 +173,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="46720125" cy="46720125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>

--- a/Week05-PreprocessingAndPipelinesSupportVectorMachines/DataScience/data_audit.xlsx
+++ b/Week05-PreprocessingAndPipelinesSupportVectorMachines/DataScience/data_audit.xlsx
@@ -198,6 +198,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7620000" cy="4762500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
